--- a/outputs/evaluation/decision/v1/CF_M08/run_2/CF_M08_decision_eval_gt_report.xlsx
+++ b/outputs/evaluation/decision/v1/CF_M08/run_2/CF_M08_decision_eval_gt_report.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -504,16 +504,16 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>AD_03</t>
+          <t>AD_01</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Traefik opens port 443 to handle HTTPS traffic, which is the standard for secure communications on the web. HTTPS encrypts the data transmitted between clients and the server, protecting the integrity and confidentiality of the information.</t>
+          <t>El puerto 80 abre para manejar tráfico HTTP redirigiéndolo al puerto 443 para asegurar que las comunicaciones se realicen de forma segura. El puerto 443 maneja el tráfico HTTPS, estándar para comunicaciones seguras que cifra los datos transmitidos entre los clientes y el servidor, protegiendo la integridad y confidencialidad.</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>0.8749</v>
+        <v>0.8267</v>
       </c>
     </row>
     <row r="3">
@@ -552,16 +552,16 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>AD_04</t>
+          <t>AD_10</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>The Component-Based pattern focuses on building the user interface by creating independent and reusable components. This approach promotes modularity, the reuse of code and maintainability, facilitating the management of the application.</t>
+          <t>El patrón Component-Based se centra en la construcción de la interfaz de usuario mediante la creación de componentes independientes y reutilizables.</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>0.584</v>
+        <v>0.5658</v>
       </c>
     </row>
     <row r="4">
@@ -600,16 +600,16 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>AD_04</t>
+          <t>AD_03</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>The Component-Based pattern focuses on building the user interface by creating independent and reusable components. This approach promotes modularity, the reuse of code and maintainability, facilitating the management of the application.</t>
+          <t>Next.js soporta tanto el renderizado de componentes en el lado del cliente (CSR) como el renderizado en el lado del servidor (SSR), utilizando las server actions para comunicar los componentes de cliente con el servidor.</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>0.5822000000000001</v>
+        <v>0.7168</v>
       </c>
     </row>
     <row r="5">
@@ -648,16 +648,16 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>AD_02</t>
+          <t>AD_03</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Traefik acts as a reverse proxy and load balancer, distributing traffic between multiple instances of a service, improving the availability and responsiveness of the application.</t>
+          <t>Next.js soporta tanto el renderizado de componentes en el lado del cliente (CSR) como el renderizado en el lado del servidor (SSR), utilizando las server actions para comunicar los componentes de cliente con el servidor.</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>0.6473</v>
+        <v>0.6203</v>
       </c>
     </row>
     <row r="6">
@@ -696,16 +696,16 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>AD_04</t>
+          <t>AD_03</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>The Component-Based pattern focuses on building the user interface by creating independent and reusable components. This approach promotes modularity, the reuse of code and maintainability, facilitating the management of the application.</t>
+          <t>Next.js soporta tanto el renderizado de componentes en el lado del cliente (CSR) como el renderizado en el lado del servidor (SSR), utilizando las server actions para comunicar los componentes de cliente con el servidor.</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>0.7005</v>
+        <v>0.7219</v>
       </c>
     </row>
     <row r="7">
@@ -734,7 +734,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Efficiency (of development); Flexibility</t>
+          <t>Efficiency; Flexibility</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -744,16 +744,16 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>AD_04</t>
+          <t>AD_10</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>The Component-Based pattern focuses on building the user interface by creating independent and reusable components. This approach promotes modularity, the reuse of code and maintainability, facilitating the management of the application.</t>
+          <t>El patrón Component-Based se centra en la construcción de la interfaz de usuario mediante la creación de componentes independientes y reutilizables.</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>0.6881</v>
+        <v>0.6884</v>
       </c>
     </row>
     <row r="8">
@@ -792,16 +792,16 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>AD_04</t>
+          <t>AD_10</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>The Component-Based pattern focuses on building the user interface by creating independent and reusable components. This approach promotes modularity, the reuse of code and maintainability, facilitating the management of the application.</t>
+          <t>El patrón Component-Based se centra en la construcción de la interfaz de usuario mediante la creación de componentes independientes y reutilizables.</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>0.7336</v>
+        <v>0.7141999999999999</v>
       </c>
     </row>
     <row r="9">
@@ -845,27 +845,27 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>The Component-Based pattern focuses on building the user interface by creating independent and reusable components. This approach promotes modularity, the reuse of code and maintainability, facilitating the management of the application.</t>
+          <t>Se comunica con el servicio de base de datos PostgreSQL (Data Service) utilizando Prisma como ORM (Object-Relational Mapping).</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>0.653</v>
+        <v>0.654</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CF_M08_AD11</t>
+          <t>CF_M08_AD12</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Prisma is compatible with several databases, including PostgreSQL, MySQL, SQLite and SQL Server.</t>
+          <t>Prisma Studio is a visual tool to explore and edit data in the database. It provides a graphical interface to visualize and manipulate the data, facilitating development and debugging.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>*CF_M08_C23</t>
+          <t>*CF_M08_C24</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -878,7 +878,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Compatibility</t>
+          <t>Depuration</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -888,64 +888,112 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>AD_01</t>
+          <t>AD_04</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>The architecture implemented for the development of the Revivack project system is a microservices-based architecture.</t>
+          <t>Se comunica con el servicio de base de datos PostgreSQL (Data Service) utilizando Prisma como ORM (Object-Relational Mapping).</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>0.5518999999999999</v>
+        <v>0.7197</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CF_M08_AD12</t>
+          <t>CF_M08_AD13</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Prisma Studio is a visual tool to explore and edit data in the database. It provides a graphical interface to visualize and manipulate the data, facilitating development and debugging.</t>
+          <t>It is generally used for manage shared resources, such as configurations, records or connections to databases data, where having multiple instances could lead to inconsistent states or usage resource inefficient.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>*CF_M08_C24</t>
+          <t>CF_M08_C06</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>CF_M08_AU09</t>
+          <t>CF_M08_P05</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Depuration</t>
+          <t>Adaptability requirements</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Prisma</t>
+          <t>Singleton</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>AD_04</t>
+          <t>AD_12</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>The Component-Based pattern focuses on building the user interface by creating independent and reusable components. This approach promotes modularity, the reuse of code and maintainability, facilitating the management of the application.</t>
+          <t>El patrón Singleton asegura que una clase tenga solo una instancia y proporciona un punto de acceso global a esa instancia. Se utiliza generalmente para gestionar recursos compartidos [...] se ha empleado, por ejemplo, para gestionar la instancia de PrismaClient</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>0.5558999999999999</v>
+        <v>0.7391</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>CF_M08_AD14</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>This approach promotes modularity, code reuse and maintainability, facilitating the management of the application</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>*CF_M08_C21, CF_M08_C05</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>CF_M08_P03</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>66</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Modularity; Maintenance Requirements</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Component-based</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>AD_10</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>El patrón Component-Based se centra en la construcción de la interfaz de usuario mediante la creación de componentes independientes y reutilizables.</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>0.7081</v>
       </c>
     </row>
   </sheetData>
